--- a/excels/M-Tech_Alumini.xlsx
+++ b/excels/M-Tech_Alumini.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{544AE952-1783-45E3-9838-36EC62D15CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB475ABF-D5B7-4A95-ACFE-67599569450B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,55 +21,56 @@
     <sheet name="1972" sheetId="62" r:id="rId6"/>
     <sheet name="1974" sheetId="7" r:id="rId7"/>
     <sheet name="1975" sheetId="8" r:id="rId8"/>
-    <sheet name="1977" sheetId="9" r:id="rId9"/>
-    <sheet name="1978" sheetId="10" r:id="rId10"/>
-    <sheet name="1979" sheetId="11" r:id="rId11"/>
-    <sheet name="1980" sheetId="12" r:id="rId12"/>
-    <sheet name="1981" sheetId="13" r:id="rId13"/>
-    <sheet name="1982" sheetId="14" r:id="rId14"/>
-    <sheet name="1983" sheetId="15" r:id="rId15"/>
-    <sheet name="1984" sheetId="16" r:id="rId16"/>
-    <sheet name="1985" sheetId="17" r:id="rId17"/>
-    <sheet name="1986" sheetId="18" r:id="rId18"/>
-    <sheet name="1987" sheetId="19" r:id="rId19"/>
-    <sheet name="1988" sheetId="20" r:id="rId20"/>
-    <sheet name="1989" sheetId="21" r:id="rId21"/>
-    <sheet name="1990" sheetId="22" r:id="rId22"/>
-    <sheet name="1991" sheetId="23" r:id="rId23"/>
-    <sheet name="1992" sheetId="24" r:id="rId24"/>
-    <sheet name="1993" sheetId="25" r:id="rId25"/>
-    <sheet name="1994" sheetId="26" r:id="rId26"/>
-    <sheet name="1995" sheetId="27" r:id="rId27"/>
-    <sheet name="1996" sheetId="28" r:id="rId28"/>
-    <sheet name="1997" sheetId="29" r:id="rId29"/>
-    <sheet name="1998" sheetId="30" r:id="rId30"/>
-    <sheet name="1999" sheetId="31" r:id="rId31"/>
-    <sheet name="2000" sheetId="32" r:id="rId32"/>
-    <sheet name="2001" sheetId="33" r:id="rId33"/>
-    <sheet name="2002" sheetId="34" r:id="rId34"/>
-    <sheet name="2003" sheetId="35" r:id="rId35"/>
-    <sheet name="2004" sheetId="36" r:id="rId36"/>
-    <sheet name="2005" sheetId="37" r:id="rId37"/>
-    <sheet name="2006" sheetId="39" r:id="rId38"/>
-    <sheet name="2007" sheetId="40" r:id="rId39"/>
-    <sheet name="2008" sheetId="41" r:id="rId40"/>
-    <sheet name="2009" sheetId="42" r:id="rId41"/>
-    <sheet name="2010" sheetId="43" r:id="rId42"/>
-    <sheet name="2011" sheetId="44" r:id="rId43"/>
-    <sheet name="2012" sheetId="45" r:id="rId44"/>
-    <sheet name="2013" sheetId="46" r:id="rId45"/>
-    <sheet name="2014" sheetId="47" r:id="rId46"/>
-    <sheet name="2015" sheetId="48" r:id="rId47"/>
-    <sheet name="2016" sheetId="49" r:id="rId48"/>
-    <sheet name="2017" sheetId="50" r:id="rId49"/>
-    <sheet name="2018" sheetId="51" r:id="rId50"/>
-    <sheet name="2019" sheetId="52" r:id="rId51"/>
-    <sheet name="2020" sheetId="53" r:id="rId52"/>
-    <sheet name="2021" sheetId="54" r:id="rId53"/>
-    <sheet name="2022" sheetId="57" r:id="rId54"/>
-    <sheet name="2023" sheetId="56" r:id="rId55"/>
-    <sheet name="2024" sheetId="55" r:id="rId56"/>
-    <sheet name="2025" sheetId="58" r:id="rId57"/>
+    <sheet name="1976" sheetId="63" r:id="rId9"/>
+    <sheet name="1977" sheetId="9" r:id="rId10"/>
+    <sheet name="1978" sheetId="10" r:id="rId11"/>
+    <sheet name="1979" sheetId="11" r:id="rId12"/>
+    <sheet name="1980" sheetId="12" r:id="rId13"/>
+    <sheet name="1981" sheetId="13" r:id="rId14"/>
+    <sheet name="1982" sheetId="14" r:id="rId15"/>
+    <sheet name="1983" sheetId="15" r:id="rId16"/>
+    <sheet name="1984" sheetId="16" r:id="rId17"/>
+    <sheet name="1985" sheetId="17" r:id="rId18"/>
+    <sheet name="1986" sheetId="18" r:id="rId19"/>
+    <sheet name="1987" sheetId="19" r:id="rId20"/>
+    <sheet name="1988" sheetId="20" r:id="rId21"/>
+    <sheet name="1989" sheetId="21" r:id="rId22"/>
+    <sheet name="1990" sheetId="22" r:id="rId23"/>
+    <sheet name="1991" sheetId="23" r:id="rId24"/>
+    <sheet name="1992" sheetId="24" r:id="rId25"/>
+    <sheet name="1993" sheetId="25" r:id="rId26"/>
+    <sheet name="1994" sheetId="26" r:id="rId27"/>
+    <sheet name="1995" sheetId="27" r:id="rId28"/>
+    <sheet name="1996" sheetId="28" r:id="rId29"/>
+    <sheet name="1997" sheetId="29" r:id="rId30"/>
+    <sheet name="1998" sheetId="30" r:id="rId31"/>
+    <sheet name="1999" sheetId="31" r:id="rId32"/>
+    <sheet name="2000" sheetId="32" r:id="rId33"/>
+    <sheet name="2001" sheetId="33" r:id="rId34"/>
+    <sheet name="2002" sheetId="34" r:id="rId35"/>
+    <sheet name="2003" sheetId="35" r:id="rId36"/>
+    <sheet name="2004" sheetId="36" r:id="rId37"/>
+    <sheet name="2005" sheetId="37" r:id="rId38"/>
+    <sheet name="2006" sheetId="39" r:id="rId39"/>
+    <sheet name="2007" sheetId="40" r:id="rId40"/>
+    <sheet name="2008" sheetId="41" r:id="rId41"/>
+    <sheet name="2009" sheetId="42" r:id="rId42"/>
+    <sheet name="2010" sheetId="43" r:id="rId43"/>
+    <sheet name="2011" sheetId="44" r:id="rId44"/>
+    <sheet name="2012" sheetId="45" r:id="rId45"/>
+    <sheet name="2013" sheetId="46" r:id="rId46"/>
+    <sheet name="2014" sheetId="47" r:id="rId47"/>
+    <sheet name="2015" sheetId="48" r:id="rId48"/>
+    <sheet name="2016" sheetId="49" r:id="rId49"/>
+    <sheet name="2017" sheetId="50" r:id="rId50"/>
+    <sheet name="2018" sheetId="51" r:id="rId51"/>
+    <sheet name="2019" sheetId="52" r:id="rId52"/>
+    <sheet name="2020" sheetId="53" r:id="rId53"/>
+    <sheet name="2021" sheetId="54" r:id="rId54"/>
+    <sheet name="2022" sheetId="57" r:id="rId55"/>
+    <sheet name="2023" sheetId="56" r:id="rId56"/>
+    <sheet name="2024" sheetId="55" r:id="rId57"/>
+    <sheet name="2025" sheetId="58" r:id="rId58"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3185" uniqueCount="2679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3193" uniqueCount="2679">
   <si>
     <t>Ramakant Jha</t>
   </si>
@@ -8601,6 +8602,87 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="88.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>160</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8700,7 +8782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8784,7 +8866,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -8935,7 +9017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -9062,7 +9144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -14200,7 +14282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -14463,7 +14545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -14825,7 +14907,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -15151,7 +15233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -15360,241 +15442,6 @@
       </c>
       <c r="F16" s="12" t="s">
         <v>403</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="24.85546875" customWidth="1"/>
-    <col min="3" max="3" width="69" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="5" max="5" width="72.42578125" customWidth="1"/>
-    <col min="6" max="6" width="36.42578125" customWidth="1"/>
-    <col min="7" max="7" width="33.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>406</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>419</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>421</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>424</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="E9" s="12" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>1736</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A13" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="E13" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>1735</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -15669,6 +15516,241 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" customWidth="1"/>
+    <col min="3" max="3" width="69" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="5" max="5" width="72.42578125" customWidth="1"/>
+    <col min="6" max="6" width="36.42578125" customWidth="1"/>
+    <col min="7" max="7" width="33.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>409</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="E9" s="12" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="C13" s="2"/>
+      <c r="E13" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>450</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -15916,7 +15998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -16136,7 +16218,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -16430,7 +16512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -16609,7 +16691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -17853,7 +17935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -18094,7 +18176,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -18263,7 +18345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -23488,7 +23570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -23729,235 +23811,6 @@
     </row>
     <row r="17" spans="8:8" ht="15.75" customHeight="1">
       <c r="H17" s="18"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A2" s="1">
-        <v>129701</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>738</v>
-      </c>
-      <c r="H2" s="19" t="s">
-        <v>2278</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A3" s="1">
-        <v>129702</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1663</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>2279</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="1">
-        <v>129703</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>740</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1664</v>
-      </c>
-      <c r="H4" s="19" t="s">
-        <v>2280</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="1">
-        <v>129704</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>741</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>2281</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="1">
-        <v>129705</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>742</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1660</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>2282</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="1">
-        <v>129706</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="H7" s="19" t="s">
-        <v>2283</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="1">
-        <v>129707</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>2284</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="1">
-        <v>129708</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1661</v>
-      </c>
-      <c r="H9" s="19" t="s">
-        <v>2285</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="1">
-        <v>129709</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1665</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>2286</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="1">
-        <v>129710</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1666</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>2287</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="1">
-        <v>129711</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1662</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>2288</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A13" s="1">
-        <v>129712</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>737</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>749</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>2289</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" s="1">
-        <v>129713</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>2290</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A15" s="1">
-        <v>129714</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>751</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>752</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>2291</v>
-      </c>
-    </row>
-    <row r="23" spans="8:8" ht="15.75" customHeight="1">
-      <c r="H23" s="19" t="s">
-        <v>943</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24050,6 +23903,235 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="1">
+        <v>129701</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>2278</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" s="1">
+        <v>129702</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>2279</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A4" s="1">
+        <v>129703</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1664</v>
+      </c>
+      <c r="H4" s="19" t="s">
+        <v>2280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A5" s="1">
+        <v>129704</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="H5" s="19" t="s">
+        <v>2281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" s="1">
+        <v>129705</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1660</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>2282</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A7" s="1">
+        <v>129706</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>2283</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="1">
+        <v>129707</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="H8" s="19" t="s">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A9" s="1">
+        <v>129708</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1661</v>
+      </c>
+      <c r="H9" s="19" t="s">
+        <v>2285</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="1">
+        <v>129709</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1665</v>
+      </c>
+      <c r="H10" s="19" t="s">
+        <v>2286</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="1">
+        <v>129710</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1666</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>2287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A12" s="1">
+        <v>129711</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>2288</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A13" s="1">
+        <v>129712</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>749</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A14" s="1">
+        <v>129713</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>750</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>2290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A15" s="1">
+        <v>129714</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>752</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>2291</v>
+      </c>
+    </row>
+    <row r="23" spans="8:8" ht="15.75" customHeight="1">
+      <c r="H23" s="19" t="s">
+        <v>943</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -24316,7 +24398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -24529,7 +24611,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -24761,7 +24843,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -25071,7 +25153,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -25370,7 +25452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -25668,7 +25750,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -25976,7 +26058,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -26284,7 +26366,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -26656,410 +26738,6 @@
       </c>
       <c r="H25" s="7" t="s">
         <v>2422</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="B26" s="6"/>
-      <c r="C26" s="14"/>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="B27" s="6"/>
-      <c r="C27" s="14"/>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="B28" s="6"/>
-      <c r="C28" s="14"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="B29" s="6"/>
-      <c r="C29" s="14"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="B30" s="6"/>
-      <c r="C30" s="14"/>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="B31" s="6"/>
-      <c r="C31" s="14"/>
-      <c r="H31" s="7"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col min="2" max="2" width="36.5703125" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A2" t="s">
-        <v>893</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="C2" s="14"/>
-      <c r="H2" s="7" t="s">
-        <v>2423</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A3" t="s">
-        <v>894</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1553</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="H3" s="7" t="s">
-        <v>2424</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" t="s">
-        <v>896</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>1558</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>2425</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" t="s">
-        <v>898</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>897</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>2141</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>2426</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" t="s">
-        <v>900</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>1567</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>2427</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" t="s">
-        <v>902</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>901</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>1557</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>2428</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" t="s">
-        <v>904</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="H8" s="7" t="s">
-        <v>2429</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" t="s">
-        <v>906</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>905</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>1562</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>2430</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" t="s">
-        <v>908</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>1554</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>2431</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" t="s">
-        <v>910</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>909</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>1561</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>2432</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" t="s">
-        <v>912</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>911</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>1556</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>2433</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A13" t="s">
-        <v>914</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>2142</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>2434</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" t="s">
-        <v>916</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>915</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>1555</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>2435</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A15" t="s">
-        <v>918</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>917</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>2143</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>2436</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A16" t="s">
-        <v>920</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>2144</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>2437</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" t="s">
-        <v>922</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>921</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>1560</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>2438</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" t="s">
-        <v>924</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>923</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>1564</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>2439</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" t="s">
-        <v>926</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>925</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>1563</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>2440</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" t="s">
-        <v>928</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>1566</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>2441</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" t="s">
-        <v>930</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>929</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>2145</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>2442</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" t="s">
-        <v>932</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>1564</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>2443</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" t="s">
-        <v>934</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>933</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>1565</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>2444</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" t="s">
-        <v>936</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>935</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>2146</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>2445</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" t="s">
-        <v>937</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>938</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>1559</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>2446</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
@@ -27174,6 +26852,410 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="36.5703125" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" t="s">
+        <v>893</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="H2" s="7" t="s">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" t="s">
+        <v>894</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C3" s="14"/>
+      <c r="H3" s="7" t="s">
+        <v>2424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A4" t="s">
+        <v>896</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>1558</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A5" t="s">
+        <v>898</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>2141</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>2426</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" t="s">
+        <v>900</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>1567</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A7" t="s">
+        <v>902</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>1557</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>2428</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" t="s">
+        <v>904</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="H8" s="7" t="s">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A9" t="s">
+        <v>906</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>1562</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>2430</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" t="s">
+        <v>908</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" t="s">
+        <v>910</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>2432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A12" t="s">
+        <v>912</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A13" t="s">
+        <v>914</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>2142</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>2434</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A14" t="s">
+        <v>916</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>1555</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A15" t="s">
+        <v>918</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>2143</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>2436</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A16" t="s">
+        <v>920</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>2144</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A17" t="s">
+        <v>922</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>1560</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>2438</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A18" t="s">
+        <v>924</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>1564</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A19" t="s">
+        <v>926</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A20" t="s">
+        <v>928</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1566</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" t="s">
+        <v>930</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>2145</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>2442</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" t="s">
+        <v>932</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>1564</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" t="s">
+        <v>934</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>1565</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>2444</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" t="s">
+        <v>936</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>2146</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A25" t="s">
+        <v>937</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>1559</v>
+      </c>
+      <c r="H25" s="19" t="s">
+        <v>2446</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="B26" s="6"/>
+      <c r="C26" s="14"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="B27" s="6"/>
+      <c r="C27" s="14"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="B28" s="6"/>
+      <c r="C28" s="14"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="B29" s="6"/>
+      <c r="C29" s="14"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="B30" s="6"/>
+      <c r="C30" s="14"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="B31" s="6"/>
+      <c r="C31" s="14"/>
+      <c r="H31" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -28611,7 +28693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -29085,7 +29167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -29510,7 +29592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -29916,7 +29998,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -30584,7 +30666,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31002,7 +31084,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31430,7 +31512,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -31841,7 +31923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -32123,313 +32205,6 @@
       <c r="C26" s="14" t="s">
         <v>1822</v>
       </c>
-      <c r="H26" s="7"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="14"/>
-      <c r="H27" s="7"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="14"/>
-      <c r="H28" s="7"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="14"/>
-      <c r="H29" s="7"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="14"/>
-      <c r="H30" s="7"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="14"/>
-      <c r="H31" s="7"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3300-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
-  <sheetData>
-    <row r="1" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A1" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6" t="s">
-        <v>1823</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>1824</v>
-      </c>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
-        <v>1825</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>1826</v>
-      </c>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>1828</v>
-      </c>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
-        <v>1829</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>1830</v>
-      </c>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6" t="s">
-        <v>1831</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>1832</v>
-      </c>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6" t="s">
-        <v>1833</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>1834</v>
-      </c>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6" t="s">
-        <v>1835</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>1836</v>
-      </c>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6" t="s">
-        <v>1837</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>1838</v>
-      </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6" t="s">
-        <v>1839</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>1840</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6" t="s">
-        <v>1841</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>1842</v>
-      </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>1844</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6" t="s">
-        <v>1845</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>1846</v>
-      </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6" t="s">
-        <v>1847</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>1848</v>
-      </c>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6" t="s">
-        <v>1849</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>1850</v>
-      </c>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6" t="s">
-        <v>1851</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>1852</v>
-      </c>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6" t="s">
-        <v>1853</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>1854</v>
-      </c>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6" t="s">
-        <v>1855</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>1856</v>
-      </c>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>1858</v>
-      </c>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6" t="s">
-        <v>1859</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>1860</v>
-      </c>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6" t="s">
-        <v>1861</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>1862</v>
-      </c>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>1864</v>
-      </c>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6" t="s">
-        <v>1865</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>1866</v>
-      </c>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="14"/>
-      <c r="H24" s="7"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="14"/>
-      <c r="H25" s="7"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="14"/>
       <c r="H26" s="7"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
@@ -32543,6 +32318,313 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3300-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A1" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>1824</v>
+      </c>
+      <c r="H2" s="7"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6" t="s">
+        <v>1825</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>1826</v>
+      </c>
+      <c r="H3" s="7"/>
+    </row>
+    <row r="4" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>1827</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>1828</v>
+      </c>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A5" s="6"/>
+      <c r="B5" s="6" t="s">
+        <v>1829</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A6" s="6"/>
+      <c r="B6" s="6" t="s">
+        <v>1831</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>1832</v>
+      </c>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6" t="s">
+        <v>1833</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A8" s="6"/>
+      <c r="B8" s="6" t="s">
+        <v>1835</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="6" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>1838</v>
+      </c>
+      <c r="H9" s="7"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A10" s="6"/>
+      <c r="B10" s="6" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H10" s="7"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6" t="s">
+        <v>1841</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>1842</v>
+      </c>
+      <c r="H11" s="7"/>
+    </row>
+    <row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6" t="s">
+        <v>1843</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>1844</v>
+      </c>
+      <c r="H12" s="7"/>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6" t="s">
+        <v>1845</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>1846</v>
+      </c>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>1848</v>
+      </c>
+      <c r="H14" s="7"/>
+    </row>
+    <row r="15" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>1852</v>
+      </c>
+      <c r="H16" s="7"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A18" s="6"/>
+      <c r="B18" s="6" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>1856</v>
+      </c>
+      <c r="H18" s="7"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6" t="s">
+        <v>1857</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>1858</v>
+      </c>
+      <c r="H19" s="7"/>
+    </row>
+    <row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A20" s="6"/>
+      <c r="B20" s="6" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H20" s="7"/>
+    </row>
+    <row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A21" s="6"/>
+      <c r="B21" s="6" t="s">
+        <v>1861</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H21" s="7"/>
+    </row>
+    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>1864</v>
+      </c>
+      <c r="H22" s="7"/>
+    </row>
+    <row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A23" s="6"/>
+      <c r="B23" s="6" t="s">
+        <v>1865</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="14"/>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="14"/>
+      <c r="H25" s="7"/>
+    </row>
+    <row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="14"/>
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A27" s="6"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="14"/>
+      <c r="H27" s="7"/>
+    </row>
+    <row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="14"/>
+      <c r="H28" s="7"/>
+    </row>
+    <row r="29" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="14"/>
+      <c r="H29" s="7"/>
+    </row>
+    <row r="30" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="14"/>
+      <c r="H30" s="7"/>
+    </row>
+    <row r="31" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="14"/>
+      <c r="H31" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -32857,7 +32939,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -33220,7 +33302,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -33546,7 +33628,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -33873,7 +33955,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -34249,7 +34331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -34646,7 +34728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -35431,7 +35513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -40063,22 +40145,9 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="69.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="88.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEDE3C8B-AD0B-49E6-B7D6-5D3D6170558D}">
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
@@ -40106,38 +40175,6 @@
         <v>140</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>1762</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="12" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>160</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excels/M-Tech_Alumini.xlsx
+++ b/excels/M-Tech_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDB7A002-E4D4-4B71-AF31-FAE919084C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B1C557-82F7-44A6-8DDB-54DD5EFDC4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="37" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1968" sheetId="4" r:id="rId1"/>
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3407" uniqueCount="2881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="2884">
   <si>
     <t>Ramakant Jha</t>
   </si>
@@ -8812,6 +8812,15 @@
   </si>
   <si>
     <t>The spectacular increase in the number of motor vehicles on thc road has created a social problem i.e. thc loss Of human lives through the road accidents. Road accidents have been a major social problem in thc developed countries of the world for fifty years. It only the fast decade the developing countries like India begun to experience large increase in the number Of road accidents taking place and have found it necessary to institute road safety programs. It is strongly felt that most of accidents, being a multi factor event, are not merely due to drivers fault on account of driver's negligence or ignorance of traffic rules and regulations, but also due to many other related factors such as abrupt changes in road conditions, flow characteristics, road user's behavior, climatic conditions, visibility and absence of traffic guidance, control and management devices. In the present study, the accident data of Rangareddy and Krishna districts of NH-9 from the year 2002-2006 was collected from concerned police stations in prepared data formats. data sheet covers all the accident details. At each police station First Information Reports are referred to note down the accident particulars. The analysis work has been carried out for NH-9 stretch which is passing through the Rangareddy and Krishna districts and black spots are identified.</t>
+  </si>
+  <si>
+    <t>Large  Scale production of automobile  after Second World Collored by increase in road haulage eave rize to nev requiremente for the roadø. Chio nev phenomenal transport denara created alarming accidentø on the exIEting roade. Thia accident rate io more in India vhen compared to other countrieg for every  1,OOO vehicle registered. It  nay be poøslbie to deøign the nov roado keeping oafety aapect in—view. But In the cage Of already existing roade it Ig only bad patcheø "known aa black opota" which require traffic Oafety measures. Traffic Safety equally applicable to both urban roada and rural road'. In this study the author hae gelected rural road of length 3B from bhongir to Uppal on Hyderauad — Waraneal road, for study Vith special reference to Bafety. Tvo uethoda VIZ. , Accident coefficient method and øafe coefficient method, Suggeøted by Prof. V.F.Bobkov have been applied to analyøo the rond for black spots. Accident data for yeare on the otretch collected and analyøed. It vao obøerved that there vaø a near co—roiatlon between the tvo. on tho analysis certain reconnendatlona voro node for Improvementø an the cue of noet øerlouø blackIn the Decond phage the author attempted to eøtablløh a relationghip between the accident coefficient and the Safe coefficient methods. Che idea that the safe coefficient method is easy and the expenøeø and labour Involved are minimum. In the Opinion of author ouch gtudieS are and have to be carried out on ail rural roads In Indin which enables in (1) deciding the exact black gpotg (2) fixing up priorities for improvement.</t>
+  </si>
+  <si>
+    <t>The succass of any urban transportation planning prognrnrno doponds upon accurate forecasting of diff- oront vehicles owned and operated by the residents tn the area. Mode split pmcedurog rost heavily on lcnovang the priori probability of ovmlng a particular vehicle by any Individual. A review of various methods for forecasting the vehide ovmerghip hag revealed that they either forecast the Past trend or by using statistical Nevertheless most of the behaviouNI models developed are appropriate only for a predominantly auto society and not applicable to developing economies. According-y, suitable hypothesis has been developed to replicate the Indian environment. Class Ificatdon techniques of multi— Statistical analysis was found to be an appro— priate tool for simulating multi-modal ownerships that are so common In a developing economy. Data for tlüs Investi gation were taken from Home-Interv1ew—Surveyg Of Roorkee town and Ænedabad metropolis. Attributeg responsible for deciding mode 01merghip of an individual were Identified and several models</t>
+  </si>
+  <si>
+    <t>Hyderabad is one of the major metropolitan cities Of India. By virtue OE tremendous growth in all sectors Of development such as industry, health, education etc., Hyderabad attracts trip makers not Only from the constiå;uent districts of Hyderabad region but also from places located outside its regional boundary. It is connected to other metro— poll tan cities of India by road, rail and air. In its 0'•m regional territory Che travel is mostly by buses because Of inadequate rail network and fre— In the absence of any foreseable quency of operation development in the railway network, in the next two decades bus vould remain the major mode of travel Eor the intra—regional trips For the assessment Of these future trips a scientific approach is necessary. conventional rrionage:rwfit:. breakeven Road Tranquor:C arc. tools for the will be for to c.cCabL1zh and would thia seudy an gather: Of p rezenz fro:a thc CICI (CES) and to rezplain the travel OE a Of Z direct aggregate demand model is found Ze ziraple eleg?ne for future level i z worked out. By means of loped a def:iciznc7 estimate OE nu:rber of bus at Is derivca and a recorcnenözl-.ion for correcting p resent deficiency is puefcrth. Traffic CES— tile years 1985, 1993 and 2001 t„zrked so as to enable the State Corporation (ESRTC) to estimate and crew requirements for these horizon years. region is devided into 25 traffic zones on thc population, urbanisation, agricultural and development, the transportation continuity. i*ne trips to each of these zones are calibrated usinq a package. Eased precent travel, Nyderabad City Region and City interaction Regions cru of the travel characteri *tics such trips income, coati Of travel, Hydera-b etc are studied to get a better of the causative factors. For a set of policy options, bus and pass— enger trips for the above horizon years are estimated. Some recommendations regarding further work needed in the di rection of estimation of comrnuter travel and r. i Zinc of bus stations are presented.</t>
   </si>
 </sst>
 </file>
@@ -9789,6 +9798,9 @@
       </c>
       <c r="C2" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2883</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>178</v>
@@ -27700,6 +27712,9 @@
       <c r="C4" s="18" t="s">
         <v>1744</v>
       </c>
+      <c r="D4" t="s">
+        <v>2881</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -41429,6 +41444,9 @@
       <c r="C2" t="s">
         <v>2879</v>
       </c>
+      <c r="D2" t="s">
+        <v>2882</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excels/M-Tech_Alumini.xlsx
+++ b/excels/M-Tech_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B1C557-82F7-44A6-8DDB-54DD5EFDC4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DBEAD4-7FAC-4D86-974A-F81ECF7E114E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="37" activeTab="43" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1968" sheetId="4" r:id="rId1"/>
@@ -8817,10 +8817,10 @@
     <t>Large  Scale production of automobile  after Second World Collored by increase in road haulage eave rize to nev requiremente for the roadø. Chio nev phenomenal transport denara created alarming accidentø on the exIEting roade. Thia accident rate io more in India vhen compared to other countrieg for every  1,OOO vehicle registered. It  nay be poøslbie to deøign the nov roado keeping oafety aapect in—view. But In the cage Of already existing roade it Ig only bad patcheø "known aa black opota" which require traffic Oafety measures. Traffic Safety equally applicable to both urban roada and rural road'. In this study the author hae gelected rural road of length 3B from bhongir to Uppal on Hyderauad — Waraneal road, for study Vith special reference to Bafety. Tvo uethoda VIZ. , Accident coefficient method and øafe coefficient method, Suggeøted by Prof. V.F.Bobkov have been applied to analyøo the rond for black spots. Accident data for yeare on the otretch collected and analyøed. It vao obøerved that there vaø a near co—roiatlon between the tvo. on tho analysis certain reconnendatlona voro node for Improvementø an the cue of noet øerlouø blackIn the Decond phage the author attempted to eøtablløh a relationghip between the accident coefficient and the Safe coefficient methods. Che idea that the safe coefficient method is easy and the expenøeø and labour Involved are minimum. In the Opinion of author ouch gtudieS are and have to be carried out on ail rural roads In Indin which enables in (1) deciding the exact black gpotg (2) fixing up priorities for improvement.</t>
   </si>
   <si>
-    <t>The succass of any urban transportation planning prognrnrno doponds upon accurate forecasting of diff- oront vehicles owned and operated by the residents tn the area. Mode split pmcedurog rost heavily on lcnovang the priori probability of ovmlng a particular vehicle by any Individual. A review of various methods for forecasting the vehide ovmerghip hag revealed that they either forecast the Past trend or by using statistical Nevertheless most of the behaviouNI models developed are appropriate only for a predominantly auto society and not applicable to developing economies. According-y, suitable hypothesis has been developed to replicate the Indian environment. Class Ificatdon techniques of multi— Statistical analysis was found to be an appro— priate tool for simulating multi-modal ownerships that are so common In a developing economy. Data for tlüs Investi gation were taken from Home-Interv1ew—Surveyg Of Roorkee town and Ænedabad metropolis. Attributeg responsible for deciding mode 01merghip of an individual were Identified and several models</t>
-  </si>
-  <si>
     <t>Hyderabad is one of the major metropolitan cities Of India. By virtue OE tremendous growth in all sectors Of development such as industry, health, education etc., Hyderabad attracts trip makers not Only from the constiå;uent districts of Hyderabad region but also from places located outside its regional boundary. It is connected to other metro— poll tan cities of India by road, rail and air. In its 0'•m regional territory Che travel is mostly by buses because Of inadequate rail network and fre— In the absence of any foreseable quency of operation development in the railway network, in the next two decades bus vould remain the major mode of travel Eor the intra—regional trips For the assessment Of these future trips a scientific approach is necessary. conventional rrionage:rwfit:. breakeven Road Tranquor:C arc. tools for the will be for to c.cCabL1zh and would thia seudy an gather: Of p rezenz fro:a thc CICI (CES) and to rezplain the travel OE a Of Z direct aggregate demand model is found Ze ziraple eleg?ne for future level i z worked out. By means of loped a def:iciznc7 estimate OE nu:rber of bus at Is derivca and a recorcnenözl-.ion for correcting p resent deficiency is puefcrth. Traffic CES— tile years 1985, 1993 and 2001 t„zrked so as to enable the State Corporation (ESRTC) to estimate and crew requirements for these horizon years. region is devided into 25 traffic zones on thc population, urbanisation, agricultural and development, the transportation continuity. i*ne trips to each of these zones are calibrated usinq a package. Eased precent travel, Nyderabad City Region and City interaction Regions cru of the travel characteri *tics such trips income, coati Of travel, Hydera-b etc are studied to get a better of the causative factors. For a set of policy options, bus and pass— enger trips for the above horizon years are estimated. Some recommendations regarding further work needed in the di rection of estimation of comrnuter travel and r. i Zinc of bus stations are presented.</t>
+  </si>
+  <si>
+    <t>The success of any urban transportation planning prognrnrno doponds upon accurate forecasting of diff- oront vehicles owned and operated by the residents tn the area. Mode split pmcedurog rost heavily on lcnovang the priori probability of ovmlng a particular vehicle by any Individual. A review of various methods for forecasting the vehide ovmerghip hag revealed that they either forecast the Past trend or by using statistical Nevertheless most of the behaviouNI models developed are appropriate only for a predominantly auto society and not applicable to developing economies. According-y, suitable hypothesis has been developed to replicate the Indian environment. Class Ificatdon techniques of multi— Statistical analysis was found to be an appro— priate tool for simulating multi-modal ownerships that are so common In a developing economy. Data for tlüs Investi gation were taken from Home-Interv1ew—Surveyg Of Roorkee town and Ænedabad metropolis. Attributeg responsible for deciding mode 01merghip of an individual were Identified and several models</t>
   </si>
 </sst>
 </file>
@@ -9800,7 +9800,7 @@
         <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>2883</v>
+        <v>2882</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>178</v>
@@ -41445,7 +41445,7 @@
         <v>2879</v>
       </c>
       <c r="D2" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
     </row>
   </sheetData>

--- a/excels/M-Tech_Alumini.xlsx
+++ b/excels/M-Tech_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93DBEAD4-7FAC-4D86-974A-F81ECF7E114E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AB9103-8C3F-4338-9B54-B2C6B9B0D71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1968" sheetId="4" r:id="rId1"/>
@@ -71,7 +71,12 @@
     <sheet name="2023" sheetId="56" r:id="rId56"/>
     <sheet name="2024" sheetId="55" r:id="rId57"/>
     <sheet name="2025" sheetId="58" r:id="rId58"/>
+    <sheet name="Sheet1" sheetId="67" r:id="rId59"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'2016'!$H$1:$H$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="49" hidden="1">'2017'!$H$1:$H$32</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -90,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3410" uniqueCount="2884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3504" uniqueCount="2977">
   <si>
     <t>Ramakant Jha</t>
   </si>
@@ -8821,6 +8826,285 @@
   </si>
   <si>
     <t>The success of any urban transportation planning prognrnrno doponds upon accurate forecasting of diff- oront vehicles owned and operated by the residents tn the area. Mode split pmcedurog rost heavily on lcnovang the priori probability of ovmlng a particular vehicle by any Individual. A review of various methods for forecasting the vehide ovmerghip hag revealed that they either forecast the Past trend or by using statistical Nevertheless most of the behaviouNI models developed are appropriate only for a predominantly auto society and not applicable to developing economies. According-y, suitable hypothesis has been developed to replicate the Indian environment. Class Ificatdon techniques of multi— Statistical analysis was found to be an appro— priate tool for simulating multi-modal ownerships that are so common In a developing economy. Data for tlüs Investi gation were taken from Home-Interv1ew—Surveyg Of Roorkee town and Ænedabad metropolis. Attributeg responsible for deciding mode 01merghip of an individual were Identified and several models</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Abhishek Sharma</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Akshay Kumar Kungulwar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Aravindmanikandan R</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Ganesh Rudrawar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Ganta Aslesha Prudhvi Raj</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Jayshree Chatterjee</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Vivek Manchikalapudi</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Mayank Rajak</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Polaki Appala Naidu</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Pooja Bhatt</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Rajkumar Singhal</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Sai Teja Tata</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Shashank Rajendra Dhanke</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Shrawan Kumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Srinivas Tatipamula</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Arun Sundar Raj M P</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/Dev Inder Sharda</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2021/N Shrikar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Ramineni Rashmitha</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Abhishek Kumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Amol Umakant Anwekar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Devendra</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Gone Sankeerthana</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Jaideep Mukherjee</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Karnati Ramya</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/K.V.N. Maheswara Raju</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Kaushik Pandey</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Shesham Koushik</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Subrat Kumar Jena</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Suyash Agrawal</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Ashar Khan</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2020/Ullam Chandu Yadav</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Akula Shyamsunder</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Bhoskar Pranav Prashant</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Cherala Shivaprasad</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Chidurala Maneesh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Divya Gautam</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Kottur Rajkumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Kuramana Ashok Kumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Lanka Geethika</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Md Zabiulla</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Mewa Prasad Sahu</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/N V Neelima</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Nandala Shiva Kumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/P. Vadde Rajasekhar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Potharaju Naveen</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Prakash Singh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Saniga. A.M.</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/S.Surya Narayana Reddy</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Satyajit Rout</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Suhail Asger</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Suhail Rashid Vaid</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/S. Venkata Sai Tharun</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2019/Vivek Yadav</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Amit Singh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Ankit Khatri</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Anoop Raj</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Arjun P V</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Asmita Subedi</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Ayush Kumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/K. Vasantha Rao</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Martha Daniel</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Mohd Tahir Ansari</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Nikhil Kumar Gupta</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Pamir</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Shuddhashil Ghosh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/S. Sudheer Kumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/V. Sreenivasulu</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2018/Vishal Behera</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Ahmad Samir Shahsamandy</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Cherupally Santoshi</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Alok Keshari</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Attada Hareesh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/G Vakula Devi</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Kundan Mandal</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Mahammad Sameer</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Meghna Gupta</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/M. Seshadri Naik</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Nawal Kishor Singh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Shubham Ghosh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Tinu Thomas</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2017/Vivek Kumar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Arun Kumar Singh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Banoth Suresh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Battula Siva Babu</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Bejjanki Ramesh</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Geddada Niranjan</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Kadagala Ramadevi</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Kali Priyo Ghosal</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Payal Kar</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Priya Pandey</t>
+  </si>
+  <si>
+    <t>Mtech_Alumini/2016/Tapas Sau</t>
   </si>
 </sst>
 </file>
@@ -8969,7 +9253,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -9042,6 +9326,18 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9328,7 +9624,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9409,7 +9705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9509,7 +9805,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9593,7 +9889,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9748,7 +10044,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -9878,7 +10174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15025,7 +15321,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15291,7 +15587,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15655,7 +15951,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -15989,7 +16285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -16310,7 +16606,7 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -16545,7 +16841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -16796,7 +17092,7 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17016,7 +17312,7 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17314,7 +17610,7 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -17493,7 +17789,7 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18737,7 +19033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -18984,7 +19280,7 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -19153,7 +19449,7 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24378,7 +24674,7 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24701,7 +24997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -24930,7 +25226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -25197,7 +25493,7 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -25410,7 +25706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -25642,7 +25938,7 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -25952,7 +26248,7 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -26254,7 +26550,7 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -26569,7 +26865,7 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -26896,7 +27192,7 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -27213,7 +27509,7 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -27722,7 +28018,7 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -28140,7 +28436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -29618,7 +29914,7 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -30116,7 +30412,7 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -30576,7 +30872,7 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -31031,7 +31327,7 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -31729,14 +32025,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B26" r:id="rId1" display="http://mithun.cm/" xr:uid="{00000000-0004-0000-2B00-000000000000}"/>
+    <hyperlink ref="B26" r:id="rId1" display="http://mithun.cm/" xr:uid="{00000000-0004-0000-2C00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2D00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -32173,7 +32469,7 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -32651,7 +32947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -33073,14 +33369,14 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B11" r:id="rId1" display="http://ramees.pm/" xr:uid="{00000000-0004-0000-2E00-000000000000}"/>
+    <hyperlink ref="B11" r:id="rId1" display="http://ramees.pm/" xr:uid="{00000000-0004-0000-2F00-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -33088,6 +33384,13 @@
   <sheetFormatPr defaultColWidth="29.140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
@@ -33134,7 +33437,10 @@
       <c r="C3" s="14" t="s">
         <v>1765</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="E3" s="6"/>
+      <c r="H3" s="6" t="s">
+        <v>2967</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="6"/>
@@ -33144,7 +33450,9 @@
       <c r="C4" s="14" t="s">
         <v>1767</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6" t="s">
+        <v>2968</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="6"/>
@@ -33154,7 +33462,9 @@
       <c r="C5" s="14" t="s">
         <v>1769</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="6" t="s">
+        <v>2969</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="6"/>
@@ -33164,7 +33474,9 @@
       <c r="C6" s="14" t="s">
         <v>1771</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="6" t="s">
+        <v>2970</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="6">
@@ -33198,7 +33510,9 @@
       <c r="C9" s="14" t="s">
         <v>1777</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="6" t="s">
+        <v>2971</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="6"/>
@@ -33228,7 +33542,9 @@
       <c r="C12" s="14" t="s">
         <v>1783</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6" t="s">
+        <v>2972</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
@@ -33238,7 +33554,9 @@
       <c r="C13" s="14" t="s">
         <v>1785</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="6" t="s">
+        <v>2973</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
@@ -33283,7 +33601,9 @@
       <c r="C17" s="14" t="s">
         <v>1793</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="6" t="s">
+        <v>2974</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="6"/>
@@ -33305,7 +33625,9 @@
       <c r="C19" s="14" t="s">
         <v>1796</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="H19" s="6" t="s">
+        <v>2975</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="6"/>
@@ -33369,7 +33691,9 @@
       <c r="C25" s="14" t="s">
         <v>1808</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="6" t="s">
+        <v>2976</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="6">
@@ -33417,6 +33741,7 @@
       <c r="H31" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="H1:H31" xr:uid="{00000000-0009-0000-0000-000030000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -33512,12 +33837,20 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.42578125" customWidth="1"/>
+    <col min="8" max="8" width="46.7109375" style="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
@@ -33541,7 +33874,7 @@
       <c r="G1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="3" t="s">
         <v>139</v>
       </c>
     </row>
@@ -33553,7 +33886,9 @@
       <c r="C2" s="14" t="s">
         <v>1812</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="6" t="s">
+        <v>2954</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="6"/>
@@ -33563,7 +33898,9 @@
       <c r="C3" s="14" t="s">
         <v>1814</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="6" t="s">
+        <v>2956</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="6">
@@ -33583,7 +33920,9 @@
       </c>
       <c r="F4" s="28"/>
       <c r="G4" s="28"/>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6" t="s">
+        <v>2957</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="6">
@@ -33627,7 +33966,9 @@
       <c r="C7" s="14" t="s">
         <v>1822</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="6" t="s">
+        <v>2958</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="6">
@@ -33642,7 +33983,9 @@
       <c r="D8" s="25" t="s">
         <v>2837</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="6" t="s">
+        <v>2955</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
@@ -33682,7 +34025,9 @@
       <c r="C12" s="14" t="s">
         <v>1830</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6" t="s">
+        <v>2959</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
@@ -33692,7 +34037,9 @@
       <c r="C13" s="14" t="s">
         <v>1832</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="6" t="s">
+        <v>2960</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
@@ -33712,7 +34059,9 @@
       <c r="C15" s="14" t="s">
         <v>1836</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="6" t="s">
+        <v>2961</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
@@ -33722,7 +34071,9 @@
       <c r="C16" s="14" t="s">
         <v>1838</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="6" t="s">
+        <v>2962</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="6"/>
@@ -33732,7 +34083,9 @@
       <c r="C17" s="14" t="s">
         <v>1840</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="6" t="s">
+        <v>2963</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="6">
@@ -33764,7 +34117,9 @@
       <c r="C20" s="14" t="s">
         <v>1846</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="6" t="s">
+        <v>2964</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="6"/>
@@ -33774,7 +34129,9 @@
       <c r="C21" s="14" t="s">
         <v>1848</v>
       </c>
-      <c r="H21" s="7"/>
+      <c r="H21" s="6" t="s">
+        <v>2965</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="6"/>
@@ -33784,7 +34141,9 @@
       <c r="C22" s="14" t="s">
         <v>1850</v>
       </c>
-      <c r="H22" s="7"/>
+      <c r="H22" s="6" t="s">
+        <v>2966</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="6"/>
@@ -33855,17 +34214,22 @@
       <c r="H32" s="7"/>
     </row>
   </sheetData>
+  <autoFilter ref="H1:H32" xr:uid="{00000000-0009-0000-0000-000031000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="2" max="2" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="32.5703125" style="37" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
@@ -33889,7 +34253,7 @@
       <c r="G1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="34" t="s">
         <v>139</v>
       </c>
     </row>
@@ -33901,7 +34265,9 @@
       <c r="C2" s="14" t="s">
         <v>1856</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="35" t="s">
+        <v>2939</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="6">
@@ -33916,7 +34282,9 @@
       <c r="E3" s="18" t="s">
         <v>2758</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="35" t="s">
+        <v>2940</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="6">
@@ -33931,7 +34299,9 @@
       <c r="E4" s="18" t="s">
         <v>2723</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="36" t="s">
+        <v>2941</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="6">
@@ -33946,7 +34316,9 @@
       <c r="E5" s="18" t="s">
         <v>2746</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="36" t="s">
+        <v>2942</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="6"/>
@@ -33956,7 +34328,9 @@
       <c r="C6" s="14" t="s">
         <v>1864</v>
       </c>
-      <c r="H6" s="7"/>
+      <c r="H6" s="36" t="s">
+        <v>2943</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="6">
@@ -33971,7 +34345,9 @@
       <c r="E7" s="18" t="s">
         <v>2704</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="36" t="s">
+        <v>2944</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
@@ -33981,7 +34357,7 @@
       <c r="C8" s="14" t="s">
         <v>1868</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="36"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
@@ -33991,7 +34367,7 @@
       <c r="C9" s="14" t="s">
         <v>1870</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="36"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="6"/>
@@ -34001,7 +34377,7 @@
       <c r="C10" s="14" t="s">
         <v>1872</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
@@ -34011,7 +34387,7 @@
       <c r="C11" s="14" t="s">
         <v>1874</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="36"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="6">
@@ -34026,7 +34402,7 @@
       <c r="E12" s="18" t="s">
         <v>2759</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="36"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="6">
@@ -34041,7 +34417,9 @@
       <c r="E13" s="18" t="s">
         <v>2729</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="36" t="s">
+        <v>2945</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="6">
@@ -34056,7 +34434,9 @@
       <c r="E14" s="18" t="s">
         <v>2710</v>
       </c>
-      <c r="H14" s="7"/>
+      <c r="H14" s="36" t="s">
+        <v>2946</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="6">
@@ -34068,7 +34448,7 @@
       <c r="C15" s="14" t="s">
         <v>1882</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="36"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="6">
@@ -34083,7 +34463,9 @@
       <c r="E16" s="18" t="s">
         <v>2742</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="36" t="s">
+        <v>2947</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="6"/>
@@ -34093,7 +34475,9 @@
       <c r="C17" s="14" t="s">
         <v>1886</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="36" t="s">
+        <v>2948</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="6"/>
@@ -34103,7 +34487,9 @@
       <c r="C18" s="14" t="s">
         <v>1888</v>
       </c>
-      <c r="H18" s="7"/>
+      <c r="H18" s="36" t="s">
+        <v>2949</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="6">
@@ -34118,7 +34504,7 @@
       <c r="E19" s="18" t="s">
         <v>2760</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="H19" s="36"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="6"/>
@@ -34128,7 +34514,7 @@
       <c r="C20" s="14" t="s">
         <v>1892</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="36"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="6">
@@ -34140,7 +34526,9 @@
       <c r="C21" s="14" t="s">
         <v>1894</v>
       </c>
-      <c r="H21" s="7"/>
+      <c r="H21" s="36" t="s">
+        <v>2950</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
       <c r="A22" s="6"/>
@@ -34150,7 +34538,9 @@
       <c r="C22" s="14" t="s">
         <v>1896</v>
       </c>
-      <c r="H22" s="7"/>
+      <c r="H22" s="36" t="s">
+        <v>2951</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="6"/>
@@ -34160,7 +34550,9 @@
       <c r="C23" s="14" t="s">
         <v>1898</v>
       </c>
-      <c r="H23" s="7"/>
+      <c r="H23" s="36" t="s">
+        <v>2952</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="6"/>
@@ -34170,7 +34562,7 @@
       <c r="C24" s="14" t="s">
         <v>1900</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="36"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="6"/>
@@ -34180,43 +34572,45 @@
       <c r="C25" s="14" t="s">
         <v>1902</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="36" t="s">
+        <v>2953</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="14"/>
-      <c r="H26" s="7"/>
+      <c r="H26" s="36"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
       <c r="B27" s="6"/>
       <c r="C27" s="14"/>
-      <c r="H27" s="7"/>
+      <c r="H27" s="36"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="14"/>
-      <c r="H28" s="7"/>
+      <c r="H28" s="36"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
       <c r="B29" s="6"/>
       <c r="C29" s="14"/>
-      <c r="H29" s="7"/>
+      <c r="H29" s="36"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="14"/>
-      <c r="H30" s="7"/>
+      <c r="H30" s="36"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="14"/>
-      <c r="H31" s="7"/>
+      <c r="H31" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34224,12 +34618,16 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:I34"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col min="7" max="7" width="16.140625" customWidth="1"/>
+    <col min="8" max="8" width="39.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
@@ -34290,7 +34688,9 @@
       <c r="E4" s="18" t="s">
         <v>2725</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6" t="s">
+        <v>2916</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="6"/>
@@ -34320,7 +34720,9 @@
       <c r="C7" s="14" t="s">
         <v>1914</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="6" t="s">
+        <v>2917</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
@@ -34330,7 +34732,9 @@
       <c r="C8" s="14" t="s">
         <v>1916</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="6" t="s">
+        <v>2918</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
@@ -34340,7 +34744,9 @@
       <c r="C9" s="14" t="s">
         <v>1918</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="6" t="s">
+        <v>2919</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="6">
@@ -34355,7 +34761,9 @@
       <c r="E10" s="18" t="s">
         <v>2741</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="6" t="s">
+        <v>2920</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
@@ -34375,7 +34783,9 @@
       <c r="C12" s="14" t="s">
         <v>1924</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6" t="s">
+        <v>2921</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
@@ -34385,7 +34795,9 @@
       <c r="C13" s="14" t="s">
         <v>1926</v>
       </c>
-      <c r="H13" s="7"/>
+      <c r="H13" s="6" t="s">
+        <v>2922</v>
+      </c>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="6"/>
@@ -34410,7 +34822,9 @@
       <c r="E15" s="18" t="s">
         <v>2740</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="6" t="s">
+        <v>2923</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="6"/>
@@ -34420,7 +34834,9 @@
       <c r="C16" s="14" t="s">
         <v>1932</v>
       </c>
-      <c r="H16" s="7"/>
+      <c r="H16" s="6" t="s">
+        <v>2924</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="15.75" customHeight="1">
       <c r="A17" s="6"/>
@@ -34430,7 +34846,9 @@
       <c r="C17" s="14" t="s">
         <v>1934</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="6" t="s">
+        <v>2925</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="15.75" customHeight="1">
       <c r="A18" s="6">
@@ -34470,7 +34888,9 @@
       <c r="E20" s="18" t="s">
         <v>2722</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="6" t="s">
+        <v>2926</v>
+      </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1">
       <c r="A21" s="6">
@@ -34485,7 +34905,9 @@
       <c r="E21" s="18" t="s">
         <v>2721</v>
       </c>
-      <c r="H21" s="7"/>
+      <c r="H21" s="6" t="s">
+        <v>2927</v>
+      </c>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1">
       <c r="A22" s="6"/>
@@ -34495,7 +34917,9 @@
       <c r="C22" s="14" t="s">
         <v>1944</v>
       </c>
-      <c r="H22" s="7"/>
+      <c r="H22" s="6" t="s">
+        <v>2928</v>
+      </c>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1">
       <c r="A23" s="6"/>
@@ -34505,7 +34929,9 @@
       <c r="C23" s="14" t="s">
         <v>1946</v>
       </c>
-      <c r="H23" s="7"/>
+      <c r="H23" s="6" t="s">
+        <v>2929</v>
+      </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1">
       <c r="A24" s="6">
@@ -34520,7 +34946,9 @@
       <c r="E24" s="18" t="s">
         <v>2744</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="6" t="s">
+        <v>2930</v>
+      </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1">
       <c r="A25" s="6"/>
@@ -34540,7 +34968,9 @@
       <c r="C26" s="14" t="s">
         <v>1952</v>
       </c>
-      <c r="H26" s="7"/>
+      <c r="H26" s="7" t="s">
+        <v>2931</v>
+      </c>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
@@ -34550,7 +34980,9 @@
       <c r="C27" s="14" t="s">
         <v>1954</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="7" t="s">
+        <v>2932</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
@@ -34560,7 +34992,9 @@
       <c r="C28" s="14" t="s">
         <v>1956</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="7" t="s">
+        <v>2933</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1">
       <c r="A29" s="6"/>
@@ -34570,7 +35004,9 @@
       <c r="C29" s="14" t="s">
         <v>1958</v>
       </c>
-      <c r="H29" s="7"/>
+      <c r="H29" s="7" t="s">
+        <v>2934</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
@@ -34580,7 +35016,9 @@
       <c r="C30" s="14" t="s">
         <v>1960</v>
       </c>
-      <c r="H30" s="7"/>
+      <c r="H30" s="7" t="s">
+        <v>2935</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1">
       <c r="A31" s="6">
@@ -34598,7 +35036,9 @@
       </c>
       <c r="F31" s="18"/>
       <c r="G31" s="18"/>
-      <c r="H31" s="1"/>
+      <c r="H31" s="1" t="s">
+        <v>2936</v>
+      </c>
       <c r="I31" s="18"/>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1">
@@ -34612,7 +35052,9 @@
       <c r="E32" s="18"/>
       <c r="F32" s="18"/>
       <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
+      <c r="H32" s="18" t="s">
+        <v>2937</v>
+      </c>
       <c r="I32" s="18"/>
     </row>
     <row r="33" spans="2:9" ht="15.75" customHeight="1">
@@ -34626,7 +35068,9 @@
       <c r="E33" s="18"/>
       <c r="F33" s="18"/>
       <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
+      <c r="H33" s="18" t="s">
+        <v>2938</v>
+      </c>
       <c r="I33" s="18"/>
     </row>
     <row r="34" spans="2:9" ht="15.75" customHeight="1">
@@ -34640,7 +35084,9 @@
       <c r="E34" s="18"/>
       <c r="F34" s="18"/>
       <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
+      <c r="H34" s="18" t="s">
+        <v>2937</v>
+      </c>
       <c r="I34" s="18"/>
     </row>
   </sheetData>
@@ -34649,7 +35095,7 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -34657,6 +35103,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="37.5703125" customWidth="1"/>
+    <col min="8" max="8" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
@@ -34693,7 +35140,9 @@
       <c r="C2" s="14" t="s">
         <v>1970</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="7" t="s">
+        <v>2902</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="6"/>
@@ -34703,7 +35152,9 @@
       <c r="C3" s="14" t="s">
         <v>1972</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="7" t="s">
+        <v>2903</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="6"/>
@@ -34713,7 +35164,7 @@
       <c r="C4" s="14" t="s">
         <v>1974</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="6">
@@ -34725,7 +35176,9 @@
       <c r="C5" s="14" t="s">
         <v>1976</v>
       </c>
-      <c r="H5" s="7"/>
+      <c r="H5" s="7" t="s">
+        <v>2904</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1">
       <c r="A6" s="6"/>
@@ -34747,7 +35200,9 @@
       <c r="C7" s="14" t="s">
         <v>1980</v>
       </c>
-      <c r="H7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>2905</v>
+      </c>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
@@ -34757,7 +35212,9 @@
       <c r="C8" s="14" t="s">
         <v>1982</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="7" t="s">
+        <v>2906</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
@@ -34767,7 +35224,9 @@
       <c r="C9" s="14" t="s">
         <v>1984</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="6" t="s">
+        <v>2907</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="6"/>
@@ -34777,7 +35236,9 @@
       <c r="C10" s="14" t="s">
         <v>1986</v>
       </c>
-      <c r="H10" s="7"/>
+      <c r="H10" s="6" t="s">
+        <v>2908</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
       <c r="A11" s="6"/>
@@ -34787,7 +35248,9 @@
       <c r="C11" s="14" t="s">
         <v>1988</v>
       </c>
-      <c r="H11" s="7"/>
+      <c r="H11" s="6" t="s">
+        <v>2909</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
@@ -34797,7 +35260,9 @@
       <c r="C12" s="14" t="s">
         <v>1990</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6" t="s">
+        <v>2910</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
@@ -34847,7 +35312,9 @@
       <c r="C17" s="14" t="s">
         <v>2000</v>
       </c>
-      <c r="H17" s="7"/>
+      <c r="H17" s="6" t="s">
+        <v>2911</v>
+      </c>
     </row>
     <row r="18" spans="1:8" ht="15.75" customHeight="1">
       <c r="A18" s="6"/>
@@ -34867,7 +35334,9 @@
       <c r="C19" s="14" t="s">
         <v>2004</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="H19" s="6" t="s">
+        <v>2912</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="6">
@@ -34882,7 +35351,9 @@
       <c r="D20" s="18" t="s">
         <v>2734</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="7" t="s">
+        <v>2913</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="6">
@@ -34930,7 +35401,9 @@
       <c r="D24" s="18" t="s">
         <v>2735</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="6" t="s">
+        <v>2914</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="6"/>
@@ -34950,7 +35423,9 @@
       <c r="C26" s="14" t="s">
         <v>2018</v>
       </c>
-      <c r="H26" s="7"/>
+      <c r="H26" s="6" t="s">
+        <v>2915</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="6"/>
@@ -35000,6 +35475,7 @@
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="38.42578125" customWidth="1"/>
+    <col min="8" max="8" width="46.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
@@ -35036,7 +35512,9 @@
       <c r="C2" s="14" t="s">
         <v>2022</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="1" t="s">
+        <v>2884</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="6"/>
@@ -35046,7 +35524,9 @@
       <c r="C3" s="14" t="s">
         <v>2024</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="1" t="s">
+        <v>2885</v>
+      </c>
     </row>
     <row r="4" spans="1:8" ht="15.75" customHeight="1">
       <c r="A4" s="6"/>
@@ -35056,7 +35536,9 @@
       <c r="C4" s="14" t="s">
         <v>2026</v>
       </c>
-      <c r="H4" s="7"/>
+      <c r="H4" s="6" t="s">
+        <v>2886</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="6"/>
@@ -35104,7 +35586,9 @@
       <c r="C8" s="14" t="s">
         <v>2034</v>
       </c>
-      <c r="H8" s="7"/>
+      <c r="H8" s="6" t="s">
+        <v>2887</v>
+      </c>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
@@ -35114,7 +35598,9 @@
       <c r="C9" s="14" t="s">
         <v>2036</v>
       </c>
-      <c r="H9" s="7"/>
+      <c r="H9" s="6" t="s">
+        <v>2888</v>
+      </c>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
@@ -35149,7 +35635,9 @@
       <c r="C12" s="14" t="s">
         <v>2042</v>
       </c>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6" t="s">
+        <v>2889</v>
+      </c>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
       <c r="A13" s="6"/>
@@ -35169,7 +35657,9 @@
       <c r="C14" s="14" t="s">
         <v>2046</v>
       </c>
-      <c r="H14" s="7"/>
+      <c r="H14" s="6" t="s">
+        <v>2890</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="6"/>
@@ -35179,7 +35669,9 @@
       <c r="C15" s="14" t="s">
         <v>2048</v>
       </c>
-      <c r="H15" s="7"/>
+      <c r="H15" s="6" t="s">
+        <v>2891</v>
+      </c>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="6" t="s">
@@ -35214,7 +35706,9 @@
       <c r="C18" s="14" t="s">
         <v>2052</v>
       </c>
-      <c r="H18" s="7"/>
+      <c r="H18" s="6" t="s">
+        <v>2892</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
       <c r="A19" s="6"/>
@@ -35224,7 +35718,9 @@
       <c r="C19" s="14" t="s">
         <v>2054</v>
       </c>
-      <c r="H19" s="7"/>
+      <c r="H19" s="6" t="s">
+        <v>2893</v>
+      </c>
     </row>
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="6"/>
@@ -35234,7 +35730,9 @@
       <c r="C20" s="14" t="s">
         <v>2056</v>
       </c>
-      <c r="H20" s="7"/>
+      <c r="H20" s="6" t="s">
+        <v>2894</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
       <c r="A21" s="6"/>
@@ -35254,7 +35752,9 @@
       <c r="C22" s="14" t="s">
         <v>2060</v>
       </c>
-      <c r="H22" s="7"/>
+      <c r="H22" s="6" t="s">
+        <v>2895</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
       <c r="A23" s="6"/>
@@ -35264,7 +35764,9 @@
       <c r="C23" s="14" t="s">
         <v>2062</v>
       </c>
-      <c r="H23" s="7"/>
+      <c r="H23" s="6" t="s">
+        <v>2896</v>
+      </c>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="6"/>
@@ -35274,7 +35776,9 @@
       <c r="C24" s="14" t="s">
         <v>2064</v>
       </c>
-      <c r="H24" s="7"/>
+      <c r="H24" s="6" t="s">
+        <v>2897</v>
+      </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="6"/>
@@ -35284,7 +35788,9 @@
       <c r="C25" s="14" t="s">
         <v>2066</v>
       </c>
-      <c r="H25" s="7"/>
+      <c r="H25" s="6" t="s">
+        <v>2898</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="6"/>
@@ -35309,7 +35815,9 @@
       <c r="D27" s="18" t="s">
         <v>2775</v>
       </c>
-      <c r="H27" s="7"/>
+      <c r="H27" s="6" t="s">
+        <v>2899</v>
+      </c>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="6"/>
@@ -35319,7 +35827,9 @@
       <c r="C28" s="14" t="s">
         <v>2072</v>
       </c>
-      <c r="H28" s="7"/>
+      <c r="H28" s="6" t="s">
+        <v>2900</v>
+      </c>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
@@ -35332,7 +35842,9 @@
         <v>2074</v>
       </c>
       <c r="D29" s="18"/>
-      <c r="H29" s="7"/>
+      <c r="H29" s="6" t="s">
+        <v>2901</v>
+      </c>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
@@ -41396,8 +41908,17 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3A00-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD7F0130-BF72-46D1-B293-8A074497C3EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -41454,7 +41975,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -41543,7 +42064,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -41705,7 +42226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData/>

--- a/excels/M-Tech_Alumini.xlsx
+++ b/excels/M-Tech_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AB9103-8C3F-4338-9B54-B2C6B9B0D71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A93936B-4FD0-4080-A5FF-21FD0DC3416A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="42" activeTab="57" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1968" sheetId="4" r:id="rId1"/>
@@ -71,7 +71,6 @@
     <sheet name="2023" sheetId="56" r:id="rId56"/>
     <sheet name="2024" sheetId="55" r:id="rId57"/>
     <sheet name="2025" sheetId="58" r:id="rId58"/>
-    <sheet name="Sheet1" sheetId="67" r:id="rId59"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="48" hidden="1">'2016'!$H$1:$H$31</definedName>
@@ -41908,15 +41907,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3A00-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H2"/>
@@ -42227,9 +42217,20 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.75" customHeight="1">
+      <c r="A1" s="3"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="5"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/excels/M-Tech_Alumini.xlsx
+++ b/excels/M-Tech_Alumini.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\nitw\NITW-Transportation-Division\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A93936B-4FD0-4080-A5FF-21FD0DC3416A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF387EB-D3FF-41F7-9DE9-23E7E0BF0C41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="42" activeTab="57" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="41" activeTab="57" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1968" sheetId="4" r:id="rId1"/>
@@ -32482,7 +32482,7 @@
     <col min="5" max="5" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
@@ -37614,12 +37614,14 @@
   <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="2" max="2" width="38.28515625" customWidth="1"/>
-    <col min="3" max="3" width="74.28515625" customWidth="1"/>
-    <col min="4" max="4" width="261" customWidth="1"/>
-    <col min="5" max="5" width="38.28515625" customWidth="1"/>
-    <col min="6" max="6" width="29.42578125" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" customHeight="1">
